--- a/output/pdf_financials_xlsx/SSV.xlsx
+++ b/output/pdf_financials_xlsx/SSV.xlsx
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.557947</v>
+        <v>-2.557947</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4.809566</v>
+        <v>-4.809566</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.116592</v>
+        <v>-1.116592</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.115764</v>
+        <v>-2.115764</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.369772</v>
+        <v>-1.369772</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3.411416</v>
+        <v>-3.411416</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2.631493</v>
+        <v>-2.631493</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>3.398722</v>
+        <v>-3.398722</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>2.49856</v>
+        <v>-2.49856</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.443331</v>
+        <v>-2.443331</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.200133</v>
+        <v>-0.200133</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>8.990615</v>
+        <v>-8.990615</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>6.32623</v>
+        <v>-6.32623</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>3.705698</v>
+        <v>-3.705698</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>5.734418</v>
+        <v>-5.734418</v>
       </c>
     </row>
     <row r="17">
@@ -1536,49 +1536,49 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.557947</v>
+        <v>-2.557947</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>4.809566</v>
+        <v>-4.809566</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.116592</v>
+        <v>-1.116592</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.115764</v>
+        <v>-2.115764</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.369772</v>
+        <v>-1.369772</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.411416</v>
+        <v>-3.411416</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2.631493</v>
+        <v>-2.631493</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.398722</v>
+        <v>-3.398722</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.49856</v>
+        <v>-2.49856</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.443331</v>
+        <v>-2.443331</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.200133</v>
+        <v>-0.200133</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>8.990615</v>
+        <v>-8.990615</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>6.32623</v>
+        <v>-6.32623</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>3.705698</v>
+        <v>-3.705698</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>5.734418</v>
+        <v>-5.734418</v>
       </c>
     </row>
     <row r="21">
@@ -1707,49 +1707,49 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.557947</v>
+        <v>-2.557947</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>4.809566</v>
+        <v>-4.809566</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.116592</v>
+        <v>-1.116592</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.115764</v>
+        <v>-2.115764</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.369772</v>
+        <v>-1.369772</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3.411416</v>
+        <v>-3.411416</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.631493</v>
+        <v>-2.631493</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>3.398722</v>
+        <v>-3.398722</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2.49856</v>
+        <v>-2.49856</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.443331</v>
+        <v>-2.443331</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.200133</v>
+        <v>-0.200133</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>8.990615</v>
+        <v>-8.990615</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>6.32623</v>
+        <v>-6.32623</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>3.705698</v>
+        <v>-3.705698</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>5.734418</v>
+        <v>-5.734418</v>
       </c>
     </row>
     <row r="24">
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>85.2649</v>
+        <v>-85.2649</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>120.23915</v>
+        <v>-120.23915</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1893,25 +1893,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>16.275108</v>
+        <v>-16.275108</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>22.829533</v>
+        <v>-22.829533</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>68.22832</v>
+        <v>-68.22832</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>87.71643299999999</v>
+        <v>-87.71643299999999</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>84.96805000000001</v>
+        <v>-84.96805000000001</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>83.28533299999999</v>
+        <v>-83.28533299999999</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>122.16655</v>
+        <v>-122.16655</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>299.687167</v>
+        <v>-299.687167</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>316.3115</v>
+        <v>-316.3115</v>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>286.7209</v>
+        <v>-286.7209</v>
       </c>
     </row>
     <row r="27">
@@ -1945,49 +1945,49 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.557947</v>
+        <v>-2.557947</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4.809566</v>
+        <v>-4.809566</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.116592</v>
+        <v>-1.116592</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.115764</v>
+        <v>-2.115764</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.369772</v>
+        <v>-1.369772</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>3.411416</v>
+        <v>-3.411416</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2.631493</v>
+        <v>-2.631493</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>3.398722</v>
+        <v>-3.398722</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.49856</v>
+        <v>-2.49856</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>2.443331</v>
+        <v>-2.443331</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.200133</v>
+        <v>-0.200133</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>8.990615</v>
+        <v>-8.990615</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>6.32623</v>
+        <v>-6.32623</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>3.705698</v>
+        <v>-3.705698</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>5.734418</v>
+        <v>-5.734418</v>
       </c>
     </row>
     <row r="28">
@@ -2059,49 +2059,49 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.557947</v>
+        <v>-2.557947</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.809566</v>
+        <v>-4.809566</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.116592</v>
+        <v>-1.116592</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.115764</v>
+        <v>-2.115764</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.369772</v>
+        <v>-1.369772</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3.411416</v>
+        <v>-3.411416</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.631493</v>
+        <v>-2.631493</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>3.398722</v>
+        <v>-3.398722</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2.49856</v>
+        <v>-2.49856</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2.443331</v>
+        <v>-2.443331</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.200133</v>
+        <v>-0.200133</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>8.990615</v>
+        <v>-8.990615</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>6.32623</v>
+        <v>-6.32623</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>3.705698</v>
+        <v>-3.705698</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>5.734418</v>
+        <v>-5.734418</v>
       </c>
     </row>
     <row r="30">
@@ -2203,49 +2203,49 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5718,49 +5718,49 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.051198</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.364041</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.120716</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.957792</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.380265</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.615601</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.767354</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.509312</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.63172</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.779732</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.225459</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>9.523137</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>8.514545999999999</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>6.740912</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>6.98073</v>
       </c>
     </row>
     <row r="93">
@@ -9280,7 +9280,11 @@
           <t>Share-based payments reserve 9</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -11454,7 +11458,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -12836,7 +12844,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -14084,7 +14096,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -18136,7 +18152,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -19200,7 +19220,11 @@
           <t>Share-based payments reserve 1,297,771</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -19294,7 +19318,11 @@
           <t>Warrants reserve 66,270</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -31825,13 +31853,13 @@
         </is>
       </c>
       <c r="R255" s="5" t="n">
-        <v>6.32623</v>
+        <v>-6.32623</v>
       </c>
       <c r="S255" s="5" t="n">
-        <v>3.705698</v>
+        <v>-3.705698</v>
       </c>
       <c r="T255" s="5" t="n">
-        <v>5.734418</v>
+        <v>-5.734418</v>
       </c>
     </row>
     <row r="256">
@@ -33238,28 +33266,28 @@
         </is>
       </c>
       <c r="K272" s="5" t="n">
-        <v>3.411416</v>
+        <v>-3.411416</v>
       </c>
       <c r="L272" s="5" t="n">
-        <v>2.631493</v>
+        <v>-2.631493</v>
       </c>
       <c r="M272" s="5" t="n">
-        <v>3.398722</v>
+        <v>-3.398722</v>
       </c>
       <c r="N272" s="5" t="n">
-        <v>2.49856</v>
+        <v>-2.49856</v>
       </c>
       <c r="O272" s="5" t="n">
-        <v>2.443331</v>
+        <v>-2.443331</v>
       </c>
       <c r="P272" s="5" t="n">
-        <v>0.200133</v>
+        <v>-0.200133</v>
       </c>
       <c r="Q272" s="5" t="n">
-        <v>8.990615</v>
+        <v>-8.990615</v>
       </c>
       <c r="R272" s="5" t="n">
-        <v>6.32623</v>
+        <v>-6.32623</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -35232,10 +35260,10 @@
         </is>
       </c>
       <c r="O293" s="5" t="n">
-        <v>2.443331</v>
+        <v>-2.443331</v>
       </c>
       <c r="P293" s="5" t="n">
-        <v>0.200133</v>
+        <v>-0.200133</v>
       </c>
       <c r="Q293" t="inlineStr">
         <is>
@@ -37183,10 +37211,10 @@
         </is>
       </c>
       <c r="J314" s="5" t="n">
-        <v>1.369772</v>
+        <v>-1.369772</v>
       </c>
       <c r="K314" s="5" t="n">
-        <v>3.411416</v>
+        <v>-3.411416</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -37468,13 +37496,13 @@
         </is>
       </c>
       <c r="I317" s="5" t="n">
-        <v>2.108764</v>
+        <v>-2.108764</v>
       </c>
       <c r="J317" s="5" t="n">
-        <v>1.374772</v>
+        <v>-1.374772</v>
       </c>
       <c r="K317" s="5" t="n">
-        <v>3.411416</v>
+        <v>-3.411416</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -38392,16 +38420,16 @@
         </is>
       </c>
       <c r="G327" s="5" t="n">
-        <v>4.809566</v>
+        <v>-4.809566</v>
       </c>
       <c r="H327" s="5" t="n">
-        <v>1.116592</v>
+        <v>-1.116592</v>
       </c>
       <c r="I327" s="5" t="n">
-        <v>2.115764</v>
+        <v>-2.115764</v>
       </c>
       <c r="J327" s="5" t="n">
-        <v>1.369772</v>
+        <v>-1.369772</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
@@ -39065,10 +39093,10 @@
         </is>
       </c>
       <c r="H334" s="5" t="n">
-        <v>1.118592</v>
+        <v>-1.118592</v>
       </c>
       <c r="I334" s="5" t="n">
-        <v>2.108764</v>
+        <v>-2.108764</v>
       </c>
       <c r="J334" t="inlineStr">
         <is>
@@ -39640,10 +39668,10 @@
         </is>
       </c>
       <c r="G340" s="5" t="n">
-        <v>4.809566</v>
+        <v>-4.809566</v>
       </c>
       <c r="H340" s="5" t="n">
-        <v>1.118592</v>
+        <v>-1.118592</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -41179,10 +41207,10 @@
         </is>
       </c>
       <c r="F356" s="5" t="n">
-        <v>2.557947</v>
+        <v>-2.557947</v>
       </c>
       <c r="G356" s="5" t="n">
-        <v>4.809566</v>
+        <v>-4.809566</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SSV.xlsx
+++ b/output/pdf_financials_xlsx/SSV.xlsx
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005382</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008869999999999999</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000283</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000249</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1945,16 +1945,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.557947</v>
+        <v>-2.552565</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.809566</v>
+        <v>-4.800696</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.116592</v>
+        <v>-1.116309</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.115764</v>
+        <v>-2.115515</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-1.369772</v>
@@ -2059,16 +2059,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.557947</v>
+        <v>-2.552565</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.809566</v>
+        <v>-4.800696</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.116592</v>
+        <v>-1.116309</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.115764</v>
+        <v>-2.115515</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.369772</v>
@@ -2354,34 +2354,34 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.656457</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.452344</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.016054</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.121247</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.063149</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.738352</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.401026</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.06049</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.376439</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>3.6416</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>7.759447</v>
@@ -2468,34 +2468,34 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.656457</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.452344</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.025054</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.016</v>
+        <v>0.137247</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.063149</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.738352</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.401026</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.06049</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.376439</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>3.6416</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>7.759447</v>
@@ -3152,34 +3152,34 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.6994359999999999</v>
+        <v>0.042979</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.472647</v>
+        <v>0.020303</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.035676</v>
+        <v>0.019622</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.153939</v>
+        <v>0.032692</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.086952</v>
+        <v>0.023803</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.784679</v>
+        <v>0.046327</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.461007</v>
+        <v>0.059981</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.112472</v>
+        <v>0.051982</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.383781</v>
+        <v>0.007342</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.698454</v>
+        <v>0.056854</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.041784</v>
@@ -13534,7 +13534,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -15288,7 +15288,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -18446,7 +18446,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -38884,7 +38884,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -40716,7 +40716,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">

--- a/output/pdf_financials_xlsx/SSV.xlsx
+++ b/output/pdf_financials_xlsx/SSV.xlsx
@@ -735,19 +735,19 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.282039</v>
+        <v>0.319791</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.545717</v>
+        <v>0.584545</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.214033</v>
+        <v>0.251706</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.191104</v>
+        <v>0.227094</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.071841</v>
+        <v>0.07784099999999999</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.19039</v>
@@ -6991,7 +6991,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.015975</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -20778,7 +20778,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -23304,7 +23308,11 @@
           <t>Proceeds from share issuance, net</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -24624,7 +24632,11 @@
           <t>Proceeds from share issuance, net</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -28122,7 +28134,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -36514,7 +36530,11 @@
           <t>Independent directors' fees 9</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -37940,7 +37960,11 @@
           <t>Independent directors' fees</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -40232,7 +40256,11 @@
           <t>Independent directors' fees 6</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
